--- a/nriss-patch-2/ig/StructureDefinition-fr-organization-document.xlsx
+++ b/nriss-patch-2/ig/StructureDefinition-fr-organization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T09:15:45+00:00</t>
+    <t>2026-10-01T07:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -493,7 +493,7 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0</t>
   </si>
   <si>
     <t>Organization.meta.security</t>
@@ -661,7 +661,7 @@
     <t>shortName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-short-name|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-short-name|2.2.0}
 </t>
   </si>
   <si>
@@ -1750,7 +1750,7 @@
 Entité Géographique : GEOGRAPHICAL-ENTITY</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-type|2.1.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-type|2.2.0</t>
   </si>
   <si>
     <t>Organization.type:organizationType.id</t>
@@ -2224,7 +2224,7 @@
     <t>Organization.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.1.0}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
@@ -2275,7 +2275,7 @@
     <t>emailType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.1.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point-email-type|2.2.0}
 </t>
   </si>
   <si>
@@ -2464,7 +2464,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.1.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.1.0)
 </t>
   </si>
   <si>
@@ -2664,7 +2664,7 @@
     <t>Organization.contact.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.1.0}
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0}
 </t>
   </si>
   <si>
